--- a/prac/2025/Soil_Data_biodiversity.xlsx
+++ b/prac/2025/Soil_Data_biodiversity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28618"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/dvdamy007_myuct_ac_za/Documents/Desktop/BIO3018F/Jasper/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasper/GIT/BIO3018F/prac/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E170023-2D97-4D90-B3B0-D867001CEA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11442DF3-611B-F043-B951-BFB4336788DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D4A98C40-3B5E-45AE-BFC8-9EB14A021E27}"/>
+    <workbookView xWindow="35720" yWindow="5940" windowWidth="24160" windowHeight="14180" xr2:uid="{D4A98C40-3B5E-45AE-BFC8-9EB14A021E27}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -35,15 +35,34 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="47">
   <si>
     <t>Site</t>
   </si>
   <si>
-    <t>Lattitude</t>
-  </si>
-  <si>
     <t>Longitude</t>
   </si>
   <si>
@@ -92,9 +111,6 @@
     <t>-34.3736111111</t>
   </si>
   <si>
-    <t>20.2175</t>
-  </si>
-  <si>
     <t>a</t>
   </si>
   <si>
@@ -125,9 +141,6 @@
     <t>C</t>
   </si>
   <si>
-    <t>-34.3830555556</t>
-  </si>
-  <si>
     <t>20.5333333333</t>
   </si>
   <si>
@@ -170,26 +183,29 @@
     <t>H</t>
   </si>
   <si>
-    <t>34.4147222222</t>
-  </si>
-  <si>
     <t>20.5730555556</t>
   </si>
   <si>
     <t>I</t>
   </si>
   <si>
-    <t>34.4172222222</t>
-  </si>
-  <si>
     <t>20.6358333333</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,15 +252,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -253,6 +271,12 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -268,12 +292,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90AB1263-AD99-4888-B6E8-67FB7EF362A9}" name="Table1" displayName="Table1" ref="A1:P41" totalsRowShown="0">
-  <autoFilter ref="A1:P41" xr:uid="{90AB1263-AD99-4888-B6E8-67FB7EF362A9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90AB1263-AD99-4888-B6E8-67FB7EF362A9}" name="Table1" displayName="Table1" ref="A1:P49" totalsRowShown="0">
+  <autoFilter ref="A1:P49" xr:uid="{90AB1263-AD99-4888-B6E8-67FB7EF362A9}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{CED53973-05CF-4702-873D-CA9C22289B60}" name="Site"/>
-    <tableColumn id="2" xr3:uid="{EF2A5905-2FA9-4239-B5F8-2D7604A81098}" name="Lattitude"/>
-    <tableColumn id="3" xr3:uid="{BCA60E9A-261B-4E75-83F0-6E767F2FB1B5}" name="Longitude"/>
+    <tableColumn id="2" xr3:uid="{EF2A5905-2FA9-4239-B5F8-2D7604A81098}" name="Latitude" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{BCA60E9A-261B-4E75-83F0-6E767F2FB1B5}" name="Longitude" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{A8AAE0A0-3C10-4EFC-A3B9-82B4285EB1AE}" name="Sample "/>
     <tableColumn id="5" xr3:uid="{FD9870D8-FF98-49EB-933C-A1DC7C9E4C02}" name="Wet Mass (1)"/>
     <tableColumn id="6" xr3:uid="{ED192EF5-AFE1-4370-8866-E3730845F209}" name=" Wet Mass (2)"/>
@@ -615,86 +639,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CAA4B68-E8B0-4171-9437-FE33225094B8}">
-  <dimension ref="A1:P41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:P49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" customWidth="1"/>
-    <col min="9" max="11" width="19.140625" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="11" width="19.1640625" customWidth="1"/>
+    <col min="12" max="12" width="17.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.1640625" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" customWidth="1"/>
+    <col min="15" max="15" width="14.1640625" customWidth="1"/>
+    <col min="16" max="16" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
+      <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="3">
+        <v>20.517499999999998</v>
+      </c>
+      <c r="D2" t="s">
         <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
       </c>
       <c r="E2">
         <v>278.72000000000003</v>
@@ -736,18 +760,18 @@
         <v>238.14666666666665</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3">
+        <v>20.517499999999998</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
       </c>
       <c r="E3">
         <v>217.81</v>
@@ -789,18 +813,18 @@
         <v>196.60333333333332</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
+      <c r="C4" s="3">
+        <v>20.517499999999998</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>258.74</v>
@@ -842,18 +866,18 @@
         <v>229.31666666666669</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
+      <c r="C5" s="3">
+        <v>20.517499999999998</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>313.7</v>
@@ -895,18 +919,18 @@
         <v>286.94333333333333</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>251.08</v>
@@ -948,18 +972,18 @@
         <v>215.05000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>300.45999999999998</v>
@@ -1001,18 +1025,18 @@
         <v>262.01333333333332</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8">
         <v>262.93</v>
@@ -1054,18 +1078,18 @@
         <v>230.18333333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>366.96</v>
@@ -1107,18 +1131,18 @@
         <v>332.68</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
-        <v>27</v>
+      <c r="B10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>383.71</v>
@@ -1160,18 +1184,18 @@
         <v>304.09333333333331</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
+      <c r="B11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11">
         <v>282.54000000000002</v>
@@ -1213,18 +1237,18 @@
         <v>235.44000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
-        <v>27</v>
+      <c r="B12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>239.03</v>
@@ -1266,18 +1290,18 @@
         <v>197.09</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" t="s">
-        <v>27</v>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13">
         <v>372.7</v>
@@ -1319,18 +1343,18 @@
         <v>302.55</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="B14" s="3">
+        <v>-34.377409999999998</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -1366,18 +1390,18 @@
         <v>101.00333333333333</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="B15" s="3">
+        <v>-34.377409999999998</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -1413,18 +1437,18 @@
         <v>189.65666666666667</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="B16" s="3">
+        <v>-34.377409999999998</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -1460,18 +1484,18 @@
         <v>176.59</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="B17" s="3">
+        <v>-34.377409999999998</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -1507,18 +1531,18 @@
         <v>79.283333333333331</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18">
         <v>205.78</v>
@@ -1560,18 +1584,18 @@
         <v>187.90666666666664</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>210.86</v>
@@ -1613,18 +1637,18 @@
         <v>185.20666666666668</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E20">
         <v>228.04</v>
@@ -1666,18 +1690,18 @@
         <v>224.18333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E21">
         <v>254.04</v>
@@ -1719,18 +1743,18 @@
         <v>241.17666666666665</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E22">
         <v>111.7</v>
@@ -1772,18 +1796,18 @@
         <v>65.44</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>104.22</v>
@@ -1825,18 +1849,18 @@
         <v>84.656666666666666</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E24">
         <v>153.82</v>
@@ -1878,18 +1902,18 @@
         <v>123.20666666666666</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E25">
         <v>158.49</v>
@@ -1931,18 +1955,18 @@
         <v>125.04</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" t="s">
-        <v>39</v>
+        <v>34</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E26">
         <v>217.82</v>
@@ -1984,18 +2008,18 @@
         <v>213.03333333333333</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" t="s">
-        <v>39</v>
+        <v>34</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E27">
         <v>222.75</v>
@@ -2037,18 +2061,18 @@
         <v>212.00666666666666</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" t="s">
-        <v>39</v>
+        <v>34</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E28">
         <v>213.01</v>
@@ -2090,18 +2114,18 @@
         <v>204.95000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" t="s">
-        <v>39</v>
+        <v>34</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E29">
         <v>176.14</v>
@@ -2143,18 +2167,18 @@
         <v>161.99666666666667</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E30">
         <v>164.68</v>
@@ -2196,18 +2220,18 @@
         <v>145.26</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E31">
         <v>243.6</v>
@@ -2249,18 +2273,18 @@
         <v>232.98666666666668</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E32">
         <v>240.25</v>
@@ -2302,18 +2326,18 @@
         <v>235.26</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E33">
         <v>396.22</v>
@@ -2355,18 +2379,18 @@
         <v>375.22333333333336</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="B34" s="3">
+        <v>-34.414722222199998</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E34">
         <v>351.59</v>
@@ -2408,18 +2432,18 @@
         <v>332.91</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="B35" s="3">
+        <v>-34.414722222199998</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E35">
         <v>259.85000000000002</v>
@@ -2461,18 +2485,18 @@
         <v>248.34333333333333</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="B36" s="3">
+        <v>-34.414722222199998</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E36">
         <v>360.14</v>
@@ -2514,18 +2538,19 @@
         <v>345.75333333333333</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" cm="1">
+        <f t="array" aca="1" ref="B37" ca="1">-Table1[[Latitude]:[Longitude]]</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E37">
         <v>317.04000000000002</v>
@@ -2567,18 +2592,18 @@
         <v>306.27</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B38" s="3">
+        <v>-34.417222222200003</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E38">
         <v>195.22</v>
@@ -2620,18 +2645,18 @@
         <v>127.50666666666666</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B39" s="3">
+        <v>-34.417222222200003</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E39">
         <v>143.75</v>
@@ -2673,18 +2698,18 @@
         <v>76.94</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B40" s="3">
+        <v>-34.417222222200003</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E40">
         <v>103.62</v>
@@ -2726,18 +2751,18 @@
         <v>65.156666666666666</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B41" s="3">
+        <v>-34.417222222200003</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E41">
         <v>63.02</v>
@@ -2777,6 +2802,190 @@
       <c r="P41">
         <f>AVERAGE(Table1[[#This Row],[Dry mass (1)]:[Dry mass (3)]])</f>
         <v>40.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3">
+        <v>-34.423650000000002</v>
+      </c>
+      <c r="C42" s="3">
+        <v>20.411797</v>
+      </c>
+      <c r="H42" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Wet Mass (1)]:[Wet Mass(3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L42" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Semi Wet Mass (1)]:[Semi Wet Mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P42" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Dry mass (1)]:[Dry mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="3">
+        <v>-34.423650000000002</v>
+      </c>
+      <c r="C43" s="3">
+        <v>20.411797</v>
+      </c>
+      <c r="H43" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Wet Mass (1)]:[Wet Mass(3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L43" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Semi Wet Mass (1)]:[Semi Wet Mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P43" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Dry mass (1)]:[Dry mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3">
+        <v>-34.423650000000002</v>
+      </c>
+      <c r="C44" s="3">
+        <v>20.411797</v>
+      </c>
+      <c r="H44" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Wet Mass (1)]:[Wet Mass(3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L44" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Semi Wet Mass (1)]:[Semi Wet Mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P44" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Dry mass (1)]:[Dry mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="3">
+        <v>-34.423650000000002</v>
+      </c>
+      <c r="C45" s="3">
+        <v>20.411797</v>
+      </c>
+      <c r="H45" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Wet Mass (1)]:[Wet Mass(3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L45" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Semi Wet Mass (1)]:[Semi Wet Mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P45" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Dry mass (1)]:[Dry mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="3">
+        <v>-34.453153</v>
+      </c>
+      <c r="C46" s="3">
+        <v>20.425028000000001</v>
+      </c>
+      <c r="H46" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Wet Mass (1)]:[Wet Mass(3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L46" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Semi Wet Mass (1)]:[Semi Wet Mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P46" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Dry mass (1)]:[Dry mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3">
+        <v>-34.453153</v>
+      </c>
+      <c r="C47" s="3">
+        <v>20.425028000000001</v>
+      </c>
+      <c r="H47" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Wet Mass (1)]:[Wet Mass(3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L47" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Semi Wet Mass (1)]:[Semi Wet Mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P47" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Dry mass (1)]:[Dry mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3">
+        <v>-34.453153</v>
+      </c>
+      <c r="C48" s="3">
+        <v>20.425028000000001</v>
+      </c>
+      <c r="H48" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Wet Mass (1)]:[Wet Mass(3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L48" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Semi Wet Mass (1)]:[Semi Wet Mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P48" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Dry mass (1)]:[Dry mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3">
+        <v>-34.453153</v>
+      </c>
+      <c r="C49" s="3">
+        <v>20.425028000000001</v>
+      </c>
+      <c r="H49" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Wet Mass (1)]:[Wet Mass(3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L49" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Semi Wet Mass (1)]:[Semi Wet Mass (3)]])</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P49" s="4" t="e">
+        <f>AVERAGE(Table1[[#This Row],[Dry mass (1)]:[Dry mass (3)]])</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
